--- a/data_lake/macro/South Korea/Employment.xlsx
+++ b/data_lake/macro/South Korea/Employment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A125C2B4-4CE4-4F03-A442-2E8EA970E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519507CA-10AC-3047-95AA-F5B3DFE929FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8EAB1BC6-7E7B-41A9-B95F-E11C960067F0}"/>
+    <workbookView xWindow="80" yWindow="780" windowWidth="23260" windowHeight="20800" xr2:uid="{8EAB1BC6-7E7B-41A9-B95F-E11C960067F0}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="2" r:id="rId1"/>
@@ -111,8 +111,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="182" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="183" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -197,10 +197,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -209,10 +206,7 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -230,10 +224,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -249,9 +249,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -289,7 +289,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -395,7 +395,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -537,7 +537,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -546,63 +546,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB197709-FD1A-4652-AD9C-303FF5E76AA2}">
   <dimension ref="B2:G4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="8.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="11">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -616,48 +616,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360F7AD4-2340-4CD7-96AA-DFAF51479F71}">
   <dimension ref="A1:G327"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="12">
         <v>36312</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="12">
         <v>36342</v>
       </c>
-      <c r="C2" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1">
@@ -667,17 +667,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="12">
         <v>36342</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="12">
         <v>36373</v>
       </c>
-      <c r="C3" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="1">
@@ -687,17 +687,17 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="12">
         <v>36373</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="12">
         <v>36404</v>
       </c>
-      <c r="C4" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1">
@@ -707,17 +707,17 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="12">
         <v>36404</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="12">
         <v>36434</v>
       </c>
-      <c r="C5" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="1">
@@ -727,17 +727,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="12">
         <v>36434</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="12">
         <v>36465</v>
       </c>
-      <c r="C6" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="1">
@@ -747,17 +747,17 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="12">
         <v>36465</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="12">
         <v>36495</v>
       </c>
-      <c r="C7" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="1">
@@ -767,17 +767,17 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
         <v>36495</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="12">
         <v>36526</v>
       </c>
-      <c r="C8" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="1">
@@ -787,17 +787,17 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="12">
         <v>36526</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="12">
         <v>36557</v>
       </c>
-      <c r="C9" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="1">
@@ -807,17 +807,17 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="12">
         <v>36557</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="12">
         <v>36586</v>
       </c>
-      <c r="C10" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="1">
@@ -827,17 +827,17 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="12">
         <v>36586</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="12">
         <v>36617</v>
       </c>
-      <c r="C11" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="1">
@@ -847,17 +847,17 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
         <v>36617</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="12">
         <v>36647</v>
       </c>
-      <c r="C12" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="1">
@@ -867,17 +867,17 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="12">
         <v>36647</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="12">
         <v>36678</v>
       </c>
-      <c r="C13" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E13" s="1">
@@ -887,17 +887,17 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="12">
         <v>36678</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="12">
         <v>36708</v>
       </c>
-      <c r="C14" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="1">
@@ -907,17 +907,17 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="12">
         <v>36708</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="12">
         <v>36739</v>
       </c>
-      <c r="C15" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="1">
@@ -927,17 +927,17 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
         <v>36739</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="12">
         <v>36770</v>
       </c>
-      <c r="C16" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="1">
@@ -947,17 +947,17 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="12">
         <v>36770</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="12">
         <v>36800</v>
       </c>
-      <c r="C17" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E17" s="1">
@@ -967,17 +967,17 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="12">
         <v>36800</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="12">
         <v>36831</v>
       </c>
-      <c r="C18" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E18" s="1">
@@ -987,17 +987,17 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="12">
         <v>36831</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="12">
         <v>36861</v>
       </c>
-      <c r="C19" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E19" s="1">
@@ -1007,17 +1007,17 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="12">
         <v>36861</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="12">
         <v>36892</v>
       </c>
-      <c r="C20" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="1">
@@ -1027,17 +1027,17 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="12">
         <v>36892</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="12">
         <v>36923</v>
       </c>
-      <c r="C21" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="1">
@@ -1047,17 +1047,17 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="12">
         <v>36923</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="12">
         <v>36951</v>
       </c>
-      <c r="C22" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E22" s="1">
@@ -1067,17 +1067,17 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="12">
         <v>36951</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="12">
         <v>36982</v>
       </c>
-      <c r="C23" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E23" s="1">
@@ -1087,17 +1087,17 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="12">
         <v>36982</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="12">
         <v>37012</v>
       </c>
-      <c r="C24" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E24" s="1">
@@ -1107,17 +1107,17 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="12">
         <v>37012</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="12">
         <v>37043</v>
       </c>
-      <c r="C25" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E25" s="1">
@@ -1127,17 +1127,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="12">
         <v>37043</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="12">
         <v>37073</v>
       </c>
-      <c r="C26" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="1">
@@ -1147,17 +1147,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="12">
         <v>37073</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="12">
         <v>37104</v>
       </c>
-      <c r="C27" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="1">
@@ -1167,17 +1167,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="12">
         <v>37104</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="12">
         <v>37135</v>
       </c>
-      <c r="C28" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E28" s="1">
@@ -1187,17 +1187,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="12">
         <v>37135</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="12">
         <v>37165</v>
       </c>
-      <c r="C29" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="C29" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E29" s="1">
@@ -1207,17 +1207,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="12">
         <v>37165</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="12">
         <v>37196</v>
       </c>
-      <c r="C30" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E30" s="1">
@@ -1227,17 +1227,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="12">
         <v>37196</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="12">
         <v>37226</v>
       </c>
-      <c r="C31" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D31" s="5" t="s">
+      <c r="C31" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="1">
@@ -1247,17 +1247,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="12">
         <v>37226</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="12">
         <v>37257</v>
       </c>
-      <c r="C32" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E32" s="1">
@@ -1267,17 +1267,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="12">
         <v>37257</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="12">
         <v>37288</v>
       </c>
-      <c r="C33" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E33" s="1">
@@ -1287,17 +1287,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="12">
         <v>37288</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="12">
         <v>37316</v>
       </c>
-      <c r="C34" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="C34" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E34" s="1">
@@ -1307,17 +1307,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="12">
         <v>37316</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="12">
         <v>37347</v>
       </c>
-      <c r="C35" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="C35" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E35" s="1">
@@ -1327,17 +1327,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="12">
         <v>37347</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="12">
         <v>37377</v>
       </c>
-      <c r="C36" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="C36" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E36" s="1">
@@ -1347,17 +1347,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="12">
         <v>37377</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="12">
         <v>37408</v>
       </c>
-      <c r="C37" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E37" s="1">
@@ -1367,17 +1367,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="12">
         <v>37408</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="12">
         <v>37438</v>
       </c>
-      <c r="C38" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="C38" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E38" s="1">
@@ -1387,17 +1387,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="12">
         <v>37438</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="12">
         <v>37469</v>
       </c>
-      <c r="C39" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="C39" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E39" s="1">
@@ -1407,17 +1407,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="12">
         <v>37469</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="12">
         <v>37500</v>
       </c>
-      <c r="C40" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D40" s="5" t="s">
+      <c r="C40" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E40" s="1">
@@ -1427,17 +1427,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="12">
         <v>37500</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="12">
         <v>37530</v>
       </c>
-      <c r="C41" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="C41" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E41" s="1">
@@ -1447,17 +1447,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="12">
         <v>37530</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="12">
         <v>37561</v>
       </c>
-      <c r="C42" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D42" s="5" t="s">
+      <c r="C42" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E42" s="1">
@@ -1467,17 +1467,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="12">
         <v>37561</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="12">
         <v>37591</v>
       </c>
-      <c r="C43" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="C43" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E43" s="1">
@@ -1487,17 +1487,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="12">
         <v>37591</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="12">
         <v>37622</v>
       </c>
-      <c r="C44" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="C44" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E44" s="1">
@@ -1507,17 +1507,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="12">
         <v>37622</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="12">
         <v>37653</v>
       </c>
-      <c r="C45" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="C45" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E45" s="1">
@@ -1527,17 +1527,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="12">
         <v>37653</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="12">
         <v>37681</v>
       </c>
-      <c r="C46" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="C46" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="1">
@@ -1547,17 +1547,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="12">
         <v>37681</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="12">
         <v>37712</v>
       </c>
-      <c r="C47" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D47" s="5" t="s">
+      <c r="C47" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E47" s="1">
@@ -1567,17 +1567,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="12">
         <v>37712</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="12">
         <v>37742</v>
       </c>
-      <c r="C48" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D48" s="5" t="s">
+      <c r="C48" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E48" s="1">
@@ -1587,17 +1587,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="12">
         <v>37742</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="12">
         <v>37773</v>
       </c>
-      <c r="C49" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D49" s="5" t="s">
+      <c r="C49" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E49" s="1">
@@ -1607,17 +1607,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="12">
         <v>37773</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="12">
         <v>37803</v>
       </c>
-      <c r="C50" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="C50" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E50" s="1">
@@ -1627,17 +1627,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="12">
         <v>37803</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="12">
         <v>37834</v>
       </c>
-      <c r="C51" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D51" s="5" t="s">
+      <c r="C51" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E51" s="1">
@@ -1647,17 +1647,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="12">
         <v>37834</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="12">
         <v>37865</v>
       </c>
-      <c r="C52" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D52" s="5" t="s">
+      <c r="C52" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E52" s="1">
@@ -1667,17 +1667,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="12">
         <v>37865</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="12">
         <v>37895</v>
       </c>
-      <c r="C53" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="C53" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E53" s="1">
@@ -1687,17 +1687,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="12">
         <v>37895</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="12">
         <v>37926</v>
       </c>
-      <c r="C54" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="C54" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E54" s="1">
@@ -1707,17 +1707,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
         <v>37926</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="12">
         <v>37956</v>
       </c>
-      <c r="C55" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="C55" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E55" s="1">
@@ -1727,17 +1727,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
         <v>37956</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="12">
         <v>37987</v>
       </c>
-      <c r="C56" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D56" s="5" t="s">
+      <c r="C56" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E56" s="1">
@@ -1747,17 +1747,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
         <v>37987</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="12">
         <v>38018</v>
       </c>
-      <c r="C57" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D57" s="5" t="s">
+      <c r="C57" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E57" s="1">
@@ -1767,17 +1767,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
         <v>38018</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="12">
         <v>38047</v>
       </c>
-      <c r="C58" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D58" s="5" t="s">
+      <c r="C58" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E58" s="1">
@@ -1787,17 +1787,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
         <v>38047</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="12">
         <v>38078</v>
       </c>
-      <c r="C59" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D59" s="5" t="s">
+      <c r="C59" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E59" s="1">
@@ -1807,17 +1807,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
         <v>38078</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="12">
         <v>38108</v>
       </c>
-      <c r="C60" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D60" s="5" t="s">
+      <c r="C60" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E60" s="1">
@@ -1827,17 +1827,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
         <v>38108</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="12">
         <v>38139</v>
       </c>
-      <c r="C61" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D61" s="5" t="s">
+      <c r="C61" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E61" s="1">
@@ -1847,17 +1847,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="12">
         <v>38139</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="12">
         <v>38169</v>
       </c>
-      <c r="C62" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D62" s="5" t="s">
+      <c r="C62" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E62" s="1">
@@ -1867,17 +1867,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="12">
         <v>38169</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="12">
         <v>38200</v>
       </c>
-      <c r="C63" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D63" s="5" t="s">
+      <c r="C63" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E63" s="1">
@@ -1887,17 +1887,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="12">
         <v>38200</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="12">
         <v>38231</v>
       </c>
-      <c r="C64" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D64" s="5" t="s">
+      <c r="C64" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E64" s="1">
@@ -1907,17 +1907,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="12">
         <v>38231</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="12">
         <v>38261</v>
       </c>
-      <c r="C65" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D65" s="5" t="s">
+      <c r="C65" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E65" s="1">
@@ -1927,17 +1927,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="12">
         <v>38261</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="12">
         <v>38292</v>
       </c>
-      <c r="C66" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D66" s="5" t="s">
+      <c r="C66" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E66" s="1">
@@ -1947,17 +1947,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="12">
         <v>38292</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="12">
         <v>38322</v>
       </c>
-      <c r="C67" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D67" s="5" t="s">
+      <c r="C67" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E67" s="1">
@@ -1967,17 +1967,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="12">
         <v>38322</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="12">
         <v>38353</v>
       </c>
-      <c r="C68" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D68" s="5" t="s">
+      <c r="C68" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E68" s="1">
@@ -1987,17 +1987,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="12">
         <v>38353</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="12">
         <v>38384</v>
       </c>
-      <c r="C69" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D69" s="5" t="s">
+      <c r="C69" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E69" s="1">
@@ -2007,17 +2007,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="12">
         <v>38384</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="12">
         <v>38412</v>
       </c>
-      <c r="C70" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D70" s="5" t="s">
+      <c r="C70" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E70" s="1">
@@ -2027,17 +2027,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="12">
         <v>38412</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="12">
         <v>38443</v>
       </c>
-      <c r="C71" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D71" s="5" t="s">
+      <c r="C71" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E71" s="1">
@@ -2047,17 +2047,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="12">
         <v>38443</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="12">
         <v>38473</v>
       </c>
-      <c r="C72" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D72" s="5" t="s">
+      <c r="C72" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E72" s="1">
@@ -2067,17 +2067,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="12">
         <v>38473</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="12">
         <v>38504</v>
       </c>
-      <c r="C73" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D73" s="5" t="s">
+      <c r="C73" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E73" s="1">
@@ -2087,17 +2087,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="12">
         <v>38504</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="12">
         <v>38534</v>
       </c>
-      <c r="C74" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D74" s="5" t="s">
+      <c r="C74" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E74" s="1">
@@ -2107,17 +2107,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="12">
         <v>38534</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="12">
         <v>38565</v>
       </c>
-      <c r="C75" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D75" s="5" t="s">
+      <c r="C75" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E75" s="1">
@@ -2127,17 +2127,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="12">
         <v>38565</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="12">
         <v>38596</v>
       </c>
-      <c r="C76" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D76" s="5" t="s">
+      <c r="C76" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E76" s="1">
@@ -2147,17 +2147,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="12">
         <v>38596</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="12">
         <v>38626</v>
       </c>
-      <c r="C77" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D77" s="5" t="s">
+      <c r="C77" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E77" s="1">
@@ -2167,17 +2167,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="12">
         <v>38626</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="12">
         <v>38657</v>
       </c>
-      <c r="C78" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D78" s="5" t="s">
+      <c r="C78" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E78" s="1">
@@ -2187,17 +2187,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="12">
         <v>38657</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="12">
         <v>38687</v>
       </c>
-      <c r="C79" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D79" s="5" t="s">
+      <c r="C79" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E79" s="1">
@@ -2207,17 +2207,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="12">
         <v>38687</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="12">
         <v>38718</v>
       </c>
-      <c r="C80" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D80" s="5" t="s">
+      <c r="C80" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E80" s="1">
@@ -2227,17 +2227,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="12">
         <v>38718</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="12">
         <v>38749</v>
       </c>
-      <c r="C81" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D81" s="5" t="s">
+      <c r="C81" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E81" s="1">
@@ -2247,17 +2247,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="12">
         <v>38749</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="12">
         <v>38777</v>
       </c>
-      <c r="C82" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D82" s="5" t="s">
+      <c r="C82" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E82" s="1">
@@ -2267,17 +2267,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="12">
         <v>38777</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="12">
         <v>38808</v>
       </c>
-      <c r="C83" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D83" s="5" t="s">
+      <c r="C83" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E83" s="1">
@@ -2287,17 +2287,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="12">
         <v>38808</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="12">
         <v>38838</v>
       </c>
-      <c r="C84" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D84" s="5" t="s">
+      <c r="C84" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E84" s="1">
@@ -2307,17 +2307,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="12">
         <v>38838</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="12">
         <v>38869</v>
       </c>
-      <c r="C85" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D85" s="5" t="s">
+      <c r="C85" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E85" s="1">
@@ -2327,17 +2327,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="12">
         <v>38869</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="12">
         <v>38899</v>
       </c>
-      <c r="C86" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D86" s="5" t="s">
+      <c r="C86" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E86" s="1">
@@ -2347,17 +2347,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="12">
         <v>38899</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="12">
         <v>38930</v>
       </c>
-      <c r="C87" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D87" s="5" t="s">
+      <c r="C87" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E87" s="1">
@@ -2367,17 +2367,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="12">
         <v>38930</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="12">
         <v>38961</v>
       </c>
-      <c r="C88" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D88" s="5" t="s">
+      <c r="C88" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E88" s="1">
@@ -2387,17 +2387,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="12">
         <v>38961</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="12">
         <v>38991</v>
       </c>
-      <c r="C89" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D89" s="5" t="s">
+      <c r="C89" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E89" s="1">
@@ -2407,17 +2407,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="12">
         <v>38991</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="12">
         <v>39022</v>
       </c>
-      <c r="C90" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D90" s="5" t="s">
+      <c r="C90" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E90" s="1">
@@ -2427,17 +2427,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="12">
         <v>39022</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="12">
         <v>39052</v>
       </c>
-      <c r="C91" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D91" s="5" t="s">
+      <c r="C91" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E91" s="1">
@@ -2447,17 +2447,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="12">
         <v>39052</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="12">
         <v>39083</v>
       </c>
-      <c r="C92" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D92" s="5" t="s">
+      <c r="C92" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E92" s="1">
@@ -2467,17 +2467,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="12">
         <v>39083</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="12">
         <v>39114</v>
       </c>
-      <c r="C93" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D93" s="5" t="s">
+      <c r="C93" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E93" s="1">
@@ -2487,17 +2487,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="12">
         <v>39114</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="12">
         <v>39142</v>
       </c>
-      <c r="C94" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D94" s="5" t="s">
+      <c r="C94" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E94" s="1">
@@ -2507,17 +2507,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="12">
         <v>39142</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="12">
         <v>39173</v>
       </c>
-      <c r="C95" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D95" s="5" t="s">
+      <c r="C95" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E95" s="1">
@@ -2527,17 +2527,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="12">
         <v>39173</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="12">
         <v>39203</v>
       </c>
-      <c r="C96" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D96" s="5" t="s">
+      <c r="C96" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E96" s="1">
@@ -2547,17 +2547,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="12">
         <v>39203</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="12">
         <v>39234</v>
       </c>
-      <c r="C97" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D97" s="5" t="s">
+      <c r="C97" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E97" s="1">
@@ -2567,17 +2567,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="12">
         <v>39234</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="12">
         <v>39264</v>
       </c>
-      <c r="C98" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D98" s="5" t="s">
+      <c r="C98" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E98" s="1">
@@ -2587,17 +2587,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="12">
         <v>39264</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="12">
         <v>39295</v>
       </c>
-      <c r="C99" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D99" s="5" t="s">
+      <c r="C99" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E99" s="1">
@@ -2607,17 +2607,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="12">
         <v>39295</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="12">
         <v>39326</v>
       </c>
-      <c r="C100" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D100" s="5" t="s">
+      <c r="C100" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E100" s="1">
@@ -2627,17 +2627,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="12">
         <v>39326</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="12">
         <v>39356</v>
       </c>
-      <c r="C101" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D101" s="5" t="s">
+      <c r="C101" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E101" s="1">
@@ -2647,17 +2647,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="12">
         <v>39356</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="12">
         <v>39387</v>
       </c>
-      <c r="C102" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D102" s="5" t="s">
+      <c r="C102" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E102" s="1">
@@ -2667,17 +2667,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="12">
         <v>39387</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="12">
         <v>39417</v>
       </c>
-      <c r="C103" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D103" s="5" t="s">
+      <c r="C103" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E103" s="1">
@@ -2687,17 +2687,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="12">
         <v>39417</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="12">
         <v>39448</v>
       </c>
-      <c r="C104" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D104" s="5" t="s">
+      <c r="C104" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E104" s="1">
@@ -2707,17 +2707,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="12">
         <v>39448</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="12">
         <v>39479</v>
       </c>
-      <c r="C105" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D105" s="5" t="s">
+      <c r="C105" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E105" s="1">
@@ -2727,17 +2727,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="12">
         <v>39479</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="12">
         <v>39508</v>
       </c>
-      <c r="C106" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D106" s="5" t="s">
+      <c r="C106" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E106" s="1">
@@ -2747,17 +2747,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="12">
         <v>39508</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="12">
         <v>39539</v>
       </c>
-      <c r="C107" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D107" s="5" t="s">
+      <c r="C107" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E107" s="1">
@@ -2767,17 +2767,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="12">
         <v>39539</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="12">
         <v>39569</v>
       </c>
-      <c r="C108" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D108" s="5" t="s">
+      <c r="C108" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E108" s="1">
@@ -2787,17 +2787,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="12">
         <v>39569</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="12">
         <v>39600</v>
       </c>
-      <c r="C109" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D109" s="5" t="s">
+      <c r="C109" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E109" s="1">
@@ -2807,17 +2807,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="12">
         <v>39600</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="12">
         <v>39630</v>
       </c>
-      <c r="C110" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D110" s="5" t="s">
+      <c r="C110" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E110" s="1">
@@ -2827,17 +2827,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="12">
         <v>39630</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="12">
         <v>39661</v>
       </c>
-      <c r="C111" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D111" s="5" t="s">
+      <c r="C111" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E111" s="1">
@@ -2847,17 +2847,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="12">
         <v>39661</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="12">
         <v>39692</v>
       </c>
-      <c r="C112" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D112" s="5" t="s">
+      <c r="C112" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E112" s="1">
@@ -2867,17 +2867,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="12">
         <v>39692</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="12">
         <v>39722</v>
       </c>
-      <c r="C113" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D113" s="5" t="s">
+      <c r="C113" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E113" s="1">
@@ -2887,17 +2887,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="12">
         <v>39722</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="12">
         <v>39753</v>
       </c>
-      <c r="C114" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D114" s="5" t="s">
+      <c r="C114" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E114" s="1">
@@ -2907,17 +2907,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="12">
         <v>39753</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="12">
         <v>39783</v>
       </c>
-      <c r="C115" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D115" s="5" t="s">
+      <c r="C115" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E115" s="1">
@@ -2927,17 +2927,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="12">
         <v>39783</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="12">
         <v>39814</v>
       </c>
-      <c r="C116" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D116" s="5" t="s">
+      <c r="C116" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E116" s="1">
@@ -2947,17 +2947,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="12">
         <v>39814</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="12">
         <v>39845</v>
       </c>
-      <c r="C117" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D117" s="5" t="s">
+      <c r="C117" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E117" s="1">
@@ -2967,17 +2967,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="12">
         <v>39845</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="12">
         <v>39873</v>
       </c>
-      <c r="C118" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D118" s="5" t="s">
+      <c r="C118" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E118" s="1">
@@ -2987,17 +2987,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="12">
         <v>39873</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="12">
         <v>39904</v>
       </c>
-      <c r="C119" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D119" s="5" t="s">
+      <c r="C119" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E119" s="1">
@@ -3007,17 +3007,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="12">
         <v>39904</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="12">
         <v>39934</v>
       </c>
-      <c r="C120" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D120" s="5" t="s">
+      <c r="C120" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E120" s="1">
@@ -3027,17 +3027,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="12">
         <v>39934</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="12">
         <v>39965</v>
       </c>
-      <c r="C121" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D121" s="5" t="s">
+      <c r="C121" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E121" s="1">
@@ -3047,17 +3047,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" s="12">
         <v>39965</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="12">
         <v>39995</v>
       </c>
-      <c r="C122" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D122" s="5" t="s">
+      <c r="C122" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E122" s="1">
@@ -3067,17 +3067,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" s="12">
         <v>39995</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="12">
         <v>40026</v>
       </c>
-      <c r="C123" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D123" s="5" t="s">
+      <c r="C123" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E123" s="1">
@@ -3087,17 +3087,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="12">
         <v>40026</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="12">
         <v>40057</v>
       </c>
-      <c r="C124" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D124" s="5" t="s">
+      <c r="C124" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E124" s="1">
@@ -3107,17 +3107,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" s="12">
         <v>40057</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="12">
         <v>40087</v>
       </c>
-      <c r="C125" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D125" s="5" t="s">
+      <c r="C125" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E125" s="1">
@@ -3127,17 +3127,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" s="12">
         <v>40087</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="12">
         <v>40118</v>
       </c>
-      <c r="C126" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D126" s="5" t="s">
+      <c r="C126" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E126" s="1">
@@ -3147,17 +3147,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" s="12">
         <v>40118</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="12">
         <v>40148</v>
       </c>
-      <c r="C127" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D127" s="5" t="s">
+      <c r="C127" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E127" s="1">
@@ -3167,17 +3167,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="12">
         <v>40148</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="12">
         <v>40179</v>
       </c>
-      <c r="C128" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D128" s="5" t="s">
+      <c r="C128" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E128" s="1">
@@ -3187,17 +3187,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="12">
         <v>40179</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="12">
         <v>40210</v>
       </c>
-      <c r="C129" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D129" s="5" t="s">
+      <c r="C129" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E129" s="1">
@@ -3207,17 +3207,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="12">
         <v>40210</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="12">
         <v>40238</v>
       </c>
-      <c r="C130" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D130" s="5" t="s">
+      <c r="C130" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E130" s="1">
@@ -3227,17 +3227,17 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="12">
         <v>40238</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="12">
         <v>40269</v>
       </c>
-      <c r="C131" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D131" s="5" t="s">
+      <c r="C131" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E131" s="1">
@@ -3247,17 +3247,17 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="12">
         <v>40269</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="12">
         <v>40299</v>
       </c>
-      <c r="C132" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D132" s="5" t="s">
+      <c r="C132" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E132" s="1">
@@ -3267,17 +3267,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="12">
         <v>40299</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="12">
         <v>40330</v>
       </c>
-      <c r="C133" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D133" s="5" t="s">
+      <c r="C133" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E133" s="1">
@@ -3287,17 +3287,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="12">
         <v>40330</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="12">
         <v>40373</v>
       </c>
-      <c r="C134" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D134" s="5" t="s">
+      <c r="C134" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E134" s="1">
@@ -3310,17 +3310,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="12">
         <v>40360</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="12">
         <v>40401</v>
       </c>
-      <c r="C135" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D135" s="5" t="s">
+      <c r="C135" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E135" s="1">
@@ -3333,17 +3333,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="12">
         <v>40391</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="12">
         <v>40436</v>
       </c>
-      <c r="C136" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D136" s="5" t="s">
+      <c r="C136" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E136" s="1">
@@ -3356,17 +3356,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="12">
         <v>40422</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="12">
         <v>40471</v>
       </c>
-      <c r="C137" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D137" s="5" t="s">
+      <c r="C137" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E137" s="1">
@@ -3379,17 +3379,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="12">
         <v>40452</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="12">
         <v>40492</v>
       </c>
-      <c r="C138" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D138" s="5" t="s">
+      <c r="C138" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E138" s="1">
@@ -3402,17 +3402,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="12">
         <v>40483</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="12">
         <v>40527</v>
       </c>
-      <c r="C139" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D139" s="5" t="s">
+      <c r="C139" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E139" s="1">
@@ -3425,17 +3425,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="12">
         <v>40513</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="12">
         <v>40555</v>
       </c>
-      <c r="C140" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D140" s="5" t="s">
+      <c r="C140" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E140" s="1">
@@ -3448,17 +3448,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="12">
         <v>40544</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="12">
         <v>40590</v>
       </c>
-      <c r="C141" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D141" s="5" t="s">
+      <c r="C141" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E141" s="1">
@@ -3471,17 +3471,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="12">
         <v>40575</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="12">
         <v>40618</v>
       </c>
-      <c r="C142" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D142" s="5" t="s">
+      <c r="C142" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D142" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E142" s="1">
@@ -3494,17 +3494,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="12">
         <v>40603</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="12">
         <v>40646</v>
       </c>
-      <c r="C143" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D143" s="5" t="s">
+      <c r="C143" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E143" s="1">
@@ -3517,17 +3517,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="12">
         <v>40634</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="12">
         <v>40674</v>
       </c>
-      <c r="C144" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D144" s="5" t="s">
+      <c r="C144" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E144" s="1">
@@ -3540,17 +3540,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="12">
         <v>40664</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="12">
         <v>40709</v>
       </c>
-      <c r="C145" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D145" s="5" t="s">
+      <c r="C145" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E145" s="1">
@@ -3563,17 +3563,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="12">
         <v>40695</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="12">
         <v>40737</v>
       </c>
-      <c r="C146" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D146" s="5" t="s">
+      <c r="C146" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E146" s="1">
@@ -3586,17 +3586,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="12">
         <v>40725</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147" s="12">
         <v>40765</v>
       </c>
-      <c r="C147" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D147" s="5" t="s">
+      <c r="C147" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E147" s="1">
@@ -3609,17 +3609,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="12">
         <v>40756</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="12">
         <v>40807</v>
       </c>
-      <c r="C148" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D148" s="5" t="s">
+      <c r="C148" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E148" s="1">
@@ -3632,17 +3632,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="12">
         <v>40787</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="12">
         <v>40828</v>
       </c>
-      <c r="C149" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D149" s="5" t="s">
+      <c r="C149" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E149" s="1">
@@ -3655,17 +3655,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="12">
         <v>40817</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="12">
         <v>40856</v>
       </c>
-      <c r="C150" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D150" s="5" t="s">
+      <c r="C150" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E150" s="1">
@@ -3678,17 +3678,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="12">
         <v>40848</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="12">
         <v>40891</v>
       </c>
-      <c r="C151" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D151" s="5" t="s">
+      <c r="C151" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E151" s="1">
@@ -3701,17 +3701,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="12">
         <v>40878</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="12">
         <v>40919</v>
       </c>
-      <c r="C152" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D152" s="5" t="s">
+      <c r="C152" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E152" s="1">
@@ -3724,17 +3724,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="12">
         <v>40909</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="12">
         <v>40954</v>
       </c>
-      <c r="C153" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D153" s="5" t="s">
+      <c r="C153" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D153" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E153" s="1">
@@ -3747,17 +3747,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="12">
         <v>40940</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154" s="12">
         <v>40982</v>
       </c>
-      <c r="C154" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D154" s="5" t="s">
+      <c r="C154" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E154" s="1">
@@ -3770,17 +3770,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="12">
         <v>40969</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="12">
         <v>41011</v>
       </c>
-      <c r="C155" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D155" s="5" t="s">
+      <c r="C155" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D155" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E155" s="1">
@@ -3793,17 +3793,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="12">
         <v>41000</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156" s="12">
         <v>41045</v>
       </c>
-      <c r="C156" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D156" s="5" t="s">
+      <c r="C156" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D156" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E156" s="1">
@@ -3816,17 +3816,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="12">
         <v>41030</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="12">
         <v>41073</v>
       </c>
-      <c r="C157" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D157" s="5" t="s">
+      <c r="C157" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E157" s="1">
@@ -3839,17 +3839,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="12">
         <v>41061</v>
       </c>
-      <c r="B158" s="2">
+      <c r="B158" s="12">
         <v>41101</v>
       </c>
-      <c r="C158" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D158" s="5" t="s">
+      <c r="C158" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D158" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E158" s="1">
@@ -3862,17 +3862,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="12">
         <v>41091</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="12">
         <v>41137</v>
       </c>
-      <c r="C159" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D159" s="5" t="s">
+      <c r="C159" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D159" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E159" s="1">
@@ -3885,17 +3885,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="12">
         <v>41122</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160" s="12">
         <v>41164</v>
       </c>
-      <c r="C160" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D160" s="5" t="s">
+      <c r="C160" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D160" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E160" s="1">
@@ -3908,17 +3908,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" s="2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="12">
         <v>41153</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="12">
         <v>41192</v>
       </c>
-      <c r="C161" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D161" s="5" t="s">
+      <c r="C161" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D161" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E161" s="1">
@@ -3931,17 +3931,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" s="2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="12">
         <v>41183</v>
       </c>
-      <c r="B162" s="2">
+      <c r="B162" s="12">
         <v>41227</v>
       </c>
-      <c r="C162" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D162" s="5" t="s">
+      <c r="C162" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D162" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E162" s="1">
@@ -3954,17 +3954,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" s="12">
         <v>41214</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163" s="12">
         <v>41255</v>
       </c>
-      <c r="C163" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D163" s="5" t="s">
+      <c r="C163" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D163" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E163" s="1">
@@ -3977,17 +3977,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" s="12">
         <v>41244</v>
       </c>
-      <c r="B164" s="2">
+      <c r="B164" s="12">
         <v>41283</v>
       </c>
-      <c r="C164" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D164" s="5" t="s">
+      <c r="C164" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D164" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E164" s="1">
@@ -4000,17 +4000,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165" s="12">
         <v>41275</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165" s="12">
         <v>41318</v>
       </c>
-      <c r="C165" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D165" s="5" t="s">
+      <c r="C165" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D165" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E165" s="1">
@@ -4023,17 +4023,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" s="2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166" s="12">
         <v>41306</v>
       </c>
-      <c r="B166" s="2">
+      <c r="B166" s="12">
         <v>41346</v>
       </c>
-      <c r="C166" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D166" s="5" t="s">
+      <c r="C166" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D166" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E166" s="1">
@@ -4046,17 +4046,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" s="2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167" s="12">
         <v>41334</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167" s="12">
         <v>41374</v>
       </c>
-      <c r="C167" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D167" s="5" t="s">
+      <c r="C167" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D167" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E167" s="1">
@@ -4069,17 +4069,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168" s="12">
         <v>41365</v>
       </c>
-      <c r="B168" s="2">
+      <c r="B168" s="12">
         <v>41409</v>
       </c>
-      <c r="C168" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D168" s="5" t="s">
+      <c r="C168" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D168" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E168" s="1">
@@ -4092,17 +4092,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" s="2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169" s="12">
         <v>41395</v>
       </c>
-      <c r="B169" s="2">
+      <c r="B169" s="12">
         <v>41437</v>
       </c>
-      <c r="C169" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D169" s="5" t="s">
+      <c r="C169" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D169" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E169" s="1">
@@ -4115,17 +4115,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" s="2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="12">
         <v>41426</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170" s="12">
         <v>41465</v>
       </c>
-      <c r="C170" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D170" s="5" t="s">
+      <c r="C170" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D170" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E170" s="1">
@@ -4138,17 +4138,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" s="2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="12">
         <v>41456</v>
       </c>
-      <c r="B171" s="2">
+      <c r="B171" s="12">
         <v>41500</v>
       </c>
-      <c r="C171" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D171" s="5" t="s">
+      <c r="C171" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E171" s="1">
@@ -4161,17 +4161,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" s="2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="12">
         <v>41487</v>
       </c>
-      <c r="B172" s="2">
+      <c r="B172" s="12">
         <v>41528</v>
       </c>
-      <c r="C172" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D172" s="5" t="s">
+      <c r="C172" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D172" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E172" s="1">
@@ -4184,17 +4184,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" s="2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="12">
         <v>41518</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B173" s="12">
         <v>41563</v>
       </c>
-      <c r="C173" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D173" s="5" t="s">
+      <c r="C173" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D173" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E173" s="1">
@@ -4207,17 +4207,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="12">
         <v>41548</v>
       </c>
-      <c r="B174" s="2">
+      <c r="B174" s="12">
         <v>41591</v>
       </c>
-      <c r="C174" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D174" s="5" t="s">
+      <c r="C174" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D174" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E174" s="1">
@@ -4230,17 +4230,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="12">
         <v>41579</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B175" s="12">
         <v>41619</v>
       </c>
-      <c r="C175" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D175" s="5" t="s">
+      <c r="C175" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E175" s="1">
@@ -4253,17 +4253,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A176" s="2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="12">
         <v>41609</v>
       </c>
-      <c r="B176" s="2">
+      <c r="B176" s="12">
         <v>41654</v>
       </c>
-      <c r="C176" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D176" s="5" t="s">
+      <c r="C176" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D176" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E176" s="1">
@@ -4276,17 +4276,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="12">
         <v>41640</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="12">
         <v>41682</v>
       </c>
-      <c r="C177" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D177" s="5" t="s">
+      <c r="C177" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D177" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E177" s="1">
@@ -4299,17 +4299,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="12">
         <v>41671</v>
       </c>
-      <c r="B178" s="2">
+      <c r="B178" s="12">
         <v>41710</v>
       </c>
-      <c r="C178" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D178" s="5" t="s">
+      <c r="C178" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D178" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E178" s="1">
@@ -4322,17 +4322,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="12">
         <v>41699</v>
       </c>
-      <c r="B179" s="2">
+      <c r="B179" s="12">
         <v>41738</v>
       </c>
-      <c r="C179" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D179" s="5" t="s">
+      <c r="C179" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D179" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E179" s="1">
@@ -4345,17 +4345,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" s="12">
         <v>41730</v>
       </c>
-      <c r="B180" s="2">
+      <c r="B180" s="12">
         <v>41773</v>
       </c>
-      <c r="C180" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D180" s="5" t="s">
+      <c r="C180" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D180" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E180" s="1">
@@ -4368,17 +4368,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181" s="12">
         <v>41760</v>
       </c>
-      <c r="B181" s="2">
+      <c r="B181" s="12">
         <v>41801</v>
       </c>
-      <c r="C181" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D181" s="5" t="s">
+      <c r="C181" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D181" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E181" s="1">
@@ -4391,17 +4391,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" s="2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182" s="12">
         <v>41791</v>
       </c>
-      <c r="B182" s="2">
+      <c r="B182" s="12">
         <v>41836</v>
       </c>
-      <c r="C182" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D182" s="5" t="s">
+      <c r="C182" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D182" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E182" s="1">
@@ -4414,17 +4414,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" s="2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183" s="12">
         <v>41821</v>
       </c>
-      <c r="B183" s="2">
+      <c r="B183" s="12">
         <v>41864</v>
       </c>
-      <c r="C183" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D183" s="5" t="s">
+      <c r="C183" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D183" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E183" s="1">
@@ -4437,17 +4437,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184" s="12">
         <v>41852</v>
       </c>
-      <c r="B184" s="2">
+      <c r="B184" s="12">
         <v>41894</v>
       </c>
-      <c r="C184" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D184" s="5" t="s">
+      <c r="C184" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D184" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E184" s="1">
@@ -4460,17 +4460,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" s="2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185" s="12">
         <v>41883</v>
       </c>
-      <c r="B185" s="2">
+      <c r="B185" s="12">
         <v>41927</v>
       </c>
-      <c r="C185" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D185" s="5" t="s">
+      <c r="C185" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D185" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E185" s="1">
@@ -4483,17 +4483,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186" s="12">
         <v>41913</v>
       </c>
-      <c r="B186" s="2">
+      <c r="B186" s="12">
         <v>41955</v>
       </c>
-      <c r="C186" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D186" s="5" t="s">
+      <c r="C186" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D186" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E186" s="1">
@@ -4506,17 +4506,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187" s="12">
         <v>41944</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="12">
         <v>41983</v>
       </c>
-      <c r="C187" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D187" s="5" t="s">
+      <c r="C187" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D187" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E187" s="1">
@@ -4529,17 +4529,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188" s="12">
         <v>41974</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188" s="12">
         <v>42018</v>
       </c>
-      <c r="C188" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D188" s="5" t="s">
+      <c r="C188" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D188" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E188" s="1">
@@ -4552,17 +4552,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189" s="12">
         <v>42005</v>
       </c>
-      <c r="B189" s="2">
+      <c r="B189" s="12">
         <v>42046</v>
       </c>
-      <c r="C189" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D189" s="5" t="s">
+      <c r="C189" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D189" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E189" s="1">
@@ -4575,17 +4575,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A190" s="12">
         <v>42036</v>
       </c>
-      <c r="B190" s="2">
+      <c r="B190" s="12">
         <v>42081</v>
       </c>
-      <c r="C190" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D190" s="5" t="s">
+      <c r="C190" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D190" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E190" s="1">
@@ -4598,17 +4598,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191" s="12">
         <v>42064</v>
       </c>
-      <c r="B191" s="2">
+      <c r="B191" s="12">
         <v>42109</v>
       </c>
-      <c r="C191" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D191" s="5" t="s">
+      <c r="C191" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D191" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E191" s="1">
@@ -4621,17 +4621,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192" s="12">
         <v>42095</v>
       </c>
-      <c r="B192" s="2">
+      <c r="B192" s="12">
         <v>42137</v>
       </c>
-      <c r="C192" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D192" s="5" t="s">
+      <c r="C192" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D192" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E192" s="1">
@@ -4644,17 +4644,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A193" s="2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A193" s="12">
         <v>42125</v>
       </c>
-      <c r="B193" s="2">
+      <c r="B193" s="12">
         <v>42165</v>
       </c>
-      <c r="C193" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D193" s="5" t="s">
+      <c r="C193" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D193" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E193" s="1">
@@ -4667,17 +4667,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" s="2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A194" s="12">
         <v>42156</v>
       </c>
-      <c r="B194" s="2">
+      <c r="B194" s="12">
         <v>42200</v>
       </c>
-      <c r="C194" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D194" s="5" t="s">
+      <c r="C194" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D194" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E194" s="1">
@@ -4690,17 +4690,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A195" s="2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A195" s="12">
         <v>42186</v>
       </c>
-      <c r="B195" s="2">
+      <c r="B195" s="12">
         <v>42228</v>
       </c>
-      <c r="C195" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D195" s="5" t="s">
+      <c r="C195" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D195" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E195" s="1">
@@ -4713,17 +4713,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A196" s="2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196" s="12">
         <v>42217</v>
       </c>
-      <c r="B196" s="2">
+      <c r="B196" s="12">
         <v>42256</v>
       </c>
-      <c r="C196" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D196" s="5" t="s">
+      <c r="C196" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D196" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E196" s="1">
@@ -4736,17 +4736,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" s="2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" s="12">
         <v>42248</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197" s="12">
         <v>42291</v>
       </c>
-      <c r="C197" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D197" s="5" t="s">
+      <c r="C197" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D197" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E197" s="1">
@@ -4759,17 +4759,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" s="12">
         <v>42278</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198" s="12">
         <v>42319</v>
       </c>
-      <c r="C198" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D198" s="5" t="s">
+      <c r="C198" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D198" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E198" s="1">
@@ -4782,17 +4782,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" s="2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199" s="12">
         <v>42309</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199" s="12">
         <v>42354</v>
       </c>
-      <c r="C199" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D199" s="5" t="s">
+      <c r="C199" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D199" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E199" s="1">
@@ -4805,17 +4805,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" s="2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200" s="12">
         <v>42339</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200" s="12">
         <v>42382</v>
       </c>
-      <c r="C200" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D200" s="5" t="s">
+      <c r="C200" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D200" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E200" s="1">
@@ -4828,17 +4828,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A201" s="2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201" s="12">
         <v>42370</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="12">
         <v>42417</v>
       </c>
-      <c r="C201" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D201" s="5" t="s">
+      <c r="C201" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D201" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E201" s="1">
@@ -4848,17 +4848,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" s="2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A202" s="12">
         <v>42401</v>
       </c>
-      <c r="B202" s="2">
+      <c r="B202" s="12">
         <v>42445</v>
       </c>
-      <c r="C202" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D202" s="5" t="s">
+      <c r="C202" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D202" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E202" s="1">
@@ -4871,17 +4871,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" s="2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A203" s="12">
         <v>42430</v>
       </c>
-      <c r="B203" s="2">
+      <c r="B203" s="12">
         <v>42475</v>
       </c>
-      <c r="C203" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D203" s="5" t="s">
+      <c r="C203" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D203" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E203" s="1">
@@ -4894,17 +4894,17 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" s="2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A204" s="12">
         <v>42461</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204" s="12">
         <v>42501</v>
       </c>
-      <c r="C204" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D204" s="5" t="s">
+      <c r="C204" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D204" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E204" s="1">
@@ -4917,17 +4917,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" s="2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A205" s="12">
         <v>42491</v>
       </c>
-      <c r="B205" s="2">
+      <c r="B205" s="12">
         <v>42536</v>
       </c>
-      <c r="C205" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D205" s="5" t="s">
+      <c r="C205" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D205" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E205" s="1">
@@ -4940,17 +4940,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A206" s="2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A206" s="12">
         <v>42522</v>
       </c>
-      <c r="B206" s="2">
+      <c r="B206" s="12">
         <v>42564</v>
       </c>
-      <c r="C206" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D206" s="5" t="s">
+      <c r="C206" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D206" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E206" s="1">
@@ -4963,17 +4963,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" s="2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A207" s="12">
         <v>42552</v>
       </c>
-      <c r="B207" s="2">
+      <c r="B207" s="12">
         <v>42592</v>
       </c>
-      <c r="C207" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D207" s="5" t="s">
+      <c r="C207" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D207" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E207" s="1">
@@ -4986,17 +4986,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" s="2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208" s="12">
         <v>42583</v>
       </c>
-      <c r="B208" s="2">
+      <c r="B208" s="12">
         <v>42626</v>
       </c>
-      <c r="C208" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D208" s="5" t="s">
+      <c r="C208" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D208" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E208" s="1">
@@ -5009,17 +5009,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" s="2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A209" s="12">
         <v>42614</v>
       </c>
-      <c r="B209" s="2">
+      <c r="B209" s="12">
         <v>42655</v>
       </c>
-      <c r="C209" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D209" s="5" t="s">
+      <c r="C209" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D209" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E209" s="1">
@@ -5032,17 +5032,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A210" s="2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A210" s="12">
         <v>42644</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210" s="12">
         <v>42683</v>
       </c>
-      <c r="C210" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D210" s="5" t="s">
+      <c r="C210" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D210" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E210" s="1">
@@ -5055,17 +5055,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" s="2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A211" s="12">
         <v>42675</v>
       </c>
-      <c r="B211" s="2">
+      <c r="B211" s="12">
         <v>42718</v>
       </c>
-      <c r="C211" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D211" s="5" t="s">
+      <c r="C211" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D211" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E211" s="1">
@@ -5075,17 +5075,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" s="2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212" s="12">
         <v>42705</v>
       </c>
-      <c r="B212" s="2">
+      <c r="B212" s="12">
         <v>42746</v>
       </c>
-      <c r="C212" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D212" s="5" t="s">
+      <c r="C212" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D212" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E212" s="1">
@@ -5095,17 +5095,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A213" s="2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" s="12">
         <v>42736</v>
       </c>
-      <c r="B213" s="2">
+      <c r="B213" s="12">
         <v>42781</v>
       </c>
-      <c r="C213" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D213" s="5" t="s">
+      <c r="C213" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D213" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E213" s="1">
@@ -5118,17 +5118,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A214" s="2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214" s="12">
         <v>42767</v>
       </c>
-      <c r="B214" s="2">
+      <c r="B214" s="12">
         <v>42809</v>
       </c>
-      <c r="C214" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D214" s="5" t="s">
+      <c r="C214" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D214" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E214" s="1">
@@ -5141,17 +5141,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" s="2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" s="12">
         <v>42795</v>
       </c>
-      <c r="B215" s="2">
+      <c r="B215" s="12">
         <v>42837</v>
       </c>
-      <c r="C215" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D215" s="5" t="s">
+      <c r="C215" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D215" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E215" s="1">
@@ -5161,17 +5161,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" s="2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" s="12">
         <v>42826</v>
       </c>
-      <c r="B216" s="2">
+      <c r="B216" s="12">
         <v>42866</v>
       </c>
-      <c r="C216" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D216" s="5" t="s">
+      <c r="C216" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D216" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E216" s="1">
@@ -5181,17 +5181,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" s="2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217" s="12">
         <v>42856</v>
       </c>
-      <c r="B217" s="2">
+      <c r="B217" s="12">
         <v>42900</v>
       </c>
-      <c r="C217" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D217" s="5" t="s">
+      <c r="C217" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D217" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E217" s="1">
@@ -5204,17 +5204,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" s="2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" s="12">
         <v>42887</v>
       </c>
-      <c r="B218" s="2">
+      <c r="B218" s="12">
         <v>42928</v>
       </c>
-      <c r="C218" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D218" s="5" t="s">
+      <c r="C218" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D218" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E218" s="1">
@@ -5224,17 +5224,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A219" s="2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A219" s="12">
         <v>42917</v>
       </c>
-      <c r="B219" s="2">
+      <c r="B219" s="12">
         <v>42956</v>
       </c>
-      <c r="C219" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D219" s="5" t="s">
+      <c r="C219" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D219" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E219" s="1">
@@ -5247,17 +5247,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A220" s="2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A220" s="12">
         <v>42948</v>
       </c>
-      <c r="B220" s="2">
+      <c r="B220" s="12">
         <v>42991</v>
       </c>
-      <c r="C220" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D220" s="5" t="s">
+      <c r="C220" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D220" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E220" s="1">
@@ -5270,17 +5270,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A221" s="2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A221" s="12">
         <v>42979</v>
       </c>
-      <c r="B221" s="2">
+      <c r="B221" s="12">
         <v>43026</v>
       </c>
-      <c r="C221" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D221" s="5" t="s">
+      <c r="C221" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D221" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E221" s="1">
@@ -5293,17 +5293,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A222" s="2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A222" s="12">
         <v>43009</v>
       </c>
-      <c r="B222" s="2">
+      <c r="B222" s="12">
         <v>43054</v>
       </c>
-      <c r="C222" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D222" s="5" t="s">
+      <c r="C222" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D222" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E222" s="1">
@@ -5316,17 +5316,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A223" s="2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A223" s="12">
         <v>43040</v>
       </c>
-      <c r="B223" s="2">
+      <c r="B223" s="12">
         <v>43082</v>
       </c>
-      <c r="C223" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D223" s="5" t="s">
+      <c r="C223" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D223" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E223" s="1">
@@ -5336,17 +5336,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A224" s="2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A224" s="12">
         <v>43070</v>
       </c>
-      <c r="B224" s="2">
+      <c r="B224" s="12">
         <v>43110</v>
       </c>
-      <c r="C224" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D224" s="5" t="s">
+      <c r="C224" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D224" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E224" s="1">
@@ -5356,17 +5356,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A225" s="2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A225" s="12">
         <v>43101</v>
       </c>
-      <c r="B225" s="2">
+      <c r="B225" s="12">
         <v>43145</v>
       </c>
-      <c r="C225" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D225" s="5" t="s">
+      <c r="C225" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D225" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E225" s="1">
@@ -5376,17 +5376,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A226" s="2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A226" s="12">
         <v>43132</v>
       </c>
-      <c r="B226" s="2">
+      <c r="B226" s="12">
         <v>43173</v>
       </c>
-      <c r="C226" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D226" s="5" t="s">
+      <c r="C226" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D226" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E226" s="1">
@@ -5396,17 +5396,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A227" s="2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A227" s="12">
         <v>43160</v>
       </c>
-      <c r="B227" s="2">
+      <c r="B227" s="12">
         <v>43201</v>
       </c>
-      <c r="C227" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D227" s="5" t="s">
+      <c r="C227" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D227" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E227" s="1">
@@ -5416,17 +5416,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A228" s="2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A228" s="12">
         <v>43191</v>
       </c>
-      <c r="B228" s="2">
+      <c r="B228" s="12">
         <v>43236</v>
       </c>
-      <c r="C228" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D228" s="5" t="s">
+      <c r="C228" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D228" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E228" s="1">
@@ -5436,17 +5436,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A229" s="2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A229" s="12">
         <v>43221</v>
       </c>
-      <c r="B229" s="2">
+      <c r="B229" s="12">
         <v>43266</v>
       </c>
-      <c r="C229" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D229" s="5" t="s">
+      <c r="C229" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D229" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E229" s="1">
@@ -5456,17 +5456,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A230" s="2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A230" s="12">
         <v>43252</v>
       </c>
-      <c r="B230" s="2">
+      <c r="B230" s="12">
         <v>43292</v>
       </c>
-      <c r="C230" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D230" s="5" t="s">
+      <c r="C230" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D230" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E230" s="1">
@@ -5476,17 +5476,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A231" s="2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A231" s="12">
         <v>43282</v>
       </c>
-      <c r="B231" s="2">
+      <c r="B231" s="12">
         <v>43329</v>
       </c>
-      <c r="C231" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D231" s="5" t="s">
+      <c r="C231" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D231" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E231" s="1">
@@ -5496,17 +5496,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A232" s="2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A232" s="12">
         <v>43313</v>
       </c>
-      <c r="B232" s="2">
+      <c r="B232" s="12">
         <v>43355</v>
       </c>
-      <c r="C232" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D232" s="5" t="s">
+      <c r="C232" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D232" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E232" s="1">
@@ -5516,17 +5516,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A233" s="2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A233" s="12">
         <v>43344</v>
       </c>
-      <c r="B233" s="2">
+      <c r="B233" s="12">
         <v>43385</v>
       </c>
-      <c r="C233" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D233" s="5" t="s">
+      <c r="C233" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D233" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E233" s="1">
@@ -5536,17 +5536,17 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A234" s="2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A234" s="12">
         <v>43374</v>
       </c>
-      <c r="B234" s="2">
+      <c r="B234" s="12">
         <v>43418</v>
       </c>
-      <c r="C234" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D234" s="5" t="s">
+      <c r="C234" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D234" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E234" s="1">
@@ -5556,17 +5556,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A235" s="2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A235" s="12">
         <v>43405</v>
       </c>
-      <c r="B235" s="2">
+      <c r="B235" s="12">
         <v>43446</v>
       </c>
-      <c r="C235" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D235" s="5" t="s">
+      <c r="C235" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D235" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E235" s="1">
@@ -5576,17 +5576,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A236" s="2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A236" s="12">
         <v>43435</v>
       </c>
-      <c r="B236" s="2">
+      <c r="B236" s="12">
         <v>43474</v>
       </c>
-      <c r="C236" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D236" s="5" t="s">
+      <c r="C236" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D236" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E236" s="1">
@@ -5596,17 +5596,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A237" s="2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A237" s="12">
         <v>43466</v>
       </c>
-      <c r="B237" s="2">
+      <c r="B237" s="12">
         <v>43509</v>
       </c>
-      <c r="C237" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D237" s="5" t="s">
+      <c r="C237" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D237" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E237" s="1">
@@ -5616,17 +5616,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A238" s="2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A238" s="12">
         <v>43497</v>
       </c>
-      <c r="B238" s="2">
+      <c r="B238" s="12">
         <v>43537</v>
       </c>
-      <c r="C238" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D238" s="5" t="s">
+      <c r="C238" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D238" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E238" s="1">
@@ -5639,17 +5639,17 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A239" s="2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A239" s="12">
         <v>43525</v>
       </c>
-      <c r="B239" s="2">
+      <c r="B239" s="12">
         <v>43565</v>
       </c>
-      <c r="C239" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D239" s="5" t="s">
+      <c r="C239" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D239" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E239" s="1">
@@ -5662,17 +5662,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A240" s="2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A240" s="12">
         <v>43556</v>
       </c>
-      <c r="B240" s="2">
+      <c r="B240" s="12">
         <v>43600</v>
       </c>
-      <c r="C240" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D240" s="5" t="s">
+      <c r="C240" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D240" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E240" s="1">
@@ -5685,17 +5685,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A241" s="2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A241" s="12">
         <v>43586</v>
       </c>
-      <c r="B241" s="2">
+      <c r="B241" s="12">
         <v>43628</v>
       </c>
-      <c r="C241" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D241" s="5" t="s">
+      <c r="C241" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D241" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E241" s="1">
@@ -5708,17 +5708,17 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A242" s="2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A242" s="12">
         <v>43617</v>
       </c>
-      <c r="B242" s="2">
+      <c r="B242" s="12">
         <v>43656</v>
       </c>
-      <c r="C242" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D242" s="5" t="s">
+      <c r="C242" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D242" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E242" s="1">
@@ -5731,17 +5731,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" s="2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A243" s="12">
         <v>43647</v>
       </c>
-      <c r="B243" s="2">
+      <c r="B243" s="12">
         <v>43691</v>
       </c>
-      <c r="C243" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D243" s="5" t="s">
+      <c r="C243" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D243" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E243" s="1">
@@ -5754,17 +5754,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A244" s="2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A244" s="12">
         <v>43678</v>
       </c>
-      <c r="B244" s="2">
+      <c r="B244" s="12">
         <v>43719</v>
       </c>
-      <c r="C244" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D244" s="5" t="s">
+      <c r="C244" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D244" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E244" s="1">
@@ -5774,17 +5774,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" s="2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A245" s="12">
         <v>43709</v>
       </c>
-      <c r="B245" s="2">
+      <c r="B245" s="12">
         <v>43754</v>
       </c>
-      <c r="C245" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D245" s="5" t="s">
+      <c r="C245" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D245" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E245" s="1">
@@ -5797,17 +5797,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" s="2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A246" s="12">
         <v>43739</v>
       </c>
-      <c r="B246" s="2">
+      <c r="B246" s="12">
         <v>43782</v>
       </c>
-      <c r="C246" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D246" s="5" t="s">
+      <c r="C246" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D246" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E246" s="1">
@@ -5817,17 +5817,17 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" s="2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A247" s="12">
         <v>43770</v>
       </c>
-      <c r="B247" s="2">
+      <c r="B247" s="12">
         <v>43810</v>
       </c>
-      <c r="C247" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D247" s="5" t="s">
+      <c r="C247" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D247" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E247" s="1">
@@ -5840,17 +5840,17 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" s="2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A248" s="12">
         <v>43800</v>
       </c>
-      <c r="B248" s="2">
+      <c r="B248" s="12">
         <v>43845</v>
       </c>
-      <c r="C248" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D248" s="5" t="s">
+      <c r="C248" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D248" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E248" s="1">
@@ -5863,17 +5863,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A249" s="12">
         <v>43831</v>
       </c>
-      <c r="B249" s="2">
+      <c r="B249" s="12">
         <v>43873</v>
       </c>
-      <c r="C249" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D249" s="5" t="s">
+      <c r="C249" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D249" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E249" s="1">
@@ -5886,17 +5886,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A250" s="12">
         <v>43862</v>
       </c>
-      <c r="B250" s="2">
+      <c r="B250" s="12">
         <v>43901</v>
       </c>
-      <c r="C250" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D250" s="5" t="s">
+      <c r="C250" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D250" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E250" s="1">
@@ -5906,17 +5906,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" s="2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A251" s="12">
         <v>43891</v>
       </c>
-      <c r="B251" s="2">
+      <c r="B251" s="12">
         <v>43938</v>
       </c>
-      <c r="C251" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D251" s="5" t="s">
+      <c r="C251" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D251" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E251" s="1">
@@ -5926,17 +5926,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A252" s="2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A252" s="12">
         <v>43922</v>
       </c>
-      <c r="B252" s="2">
+      <c r="B252" s="12">
         <v>43964</v>
       </c>
-      <c r="C252" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D252" s="5" t="s">
+      <c r="C252" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D252" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E252" s="1">
@@ -5946,17 +5946,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" s="2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A253" s="12">
         <v>43952</v>
       </c>
-      <c r="B253" s="2">
+      <c r="B253" s="12">
         <v>43992</v>
       </c>
-      <c r="C253" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D253" s="5" t="s">
+      <c r="C253" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D253" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E253" s="1">
@@ -5966,17 +5966,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A254" s="2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A254" s="12">
         <v>43983</v>
       </c>
-      <c r="B254" s="2">
+      <c r="B254" s="12">
         <v>44027</v>
       </c>
-      <c r="C254" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D254" s="5" t="s">
+      <c r="C254" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D254" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E254" s="1">
@@ -5986,17 +5986,17 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A255" s="2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A255" s="12">
         <v>44013</v>
       </c>
-      <c r="B255" s="2">
+      <c r="B255" s="12">
         <v>44055</v>
       </c>
-      <c r="C255" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D255" s="5" t="s">
+      <c r="C255" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D255" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E255" s="1">
@@ -6009,17 +6009,17 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" s="2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A256" s="12">
         <v>44044</v>
       </c>
-      <c r="B256" s="2">
+      <c r="B256" s="12">
         <v>44083</v>
       </c>
-      <c r="C256" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D256" s="5" t="s">
+      <c r="C256" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D256" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E256" s="1">
@@ -6029,17 +6029,17 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A257" s="2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A257" s="12">
         <v>44075</v>
       </c>
-      <c r="B257" s="2">
+      <c r="B257" s="12">
         <v>44120</v>
       </c>
-      <c r="C257" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D257" s="5" t="s">
+      <c r="C257" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D257" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E257" s="1">
@@ -6049,17 +6049,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A258" s="2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A258" s="12">
         <v>44105</v>
       </c>
-      <c r="B258" s="2">
+      <c r="B258" s="12">
         <v>44146</v>
       </c>
-      <c r="C258" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D258" s="5" t="s">
+      <c r="C258" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D258" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E258" s="1">
@@ -6069,17 +6069,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A259" s="2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A259" s="12">
         <v>44136</v>
       </c>
-      <c r="B259" s="2">
+      <c r="B259" s="12">
         <v>44181</v>
       </c>
-      <c r="C259" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D259" s="5" t="s">
+      <c r="C259" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D259" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E259" s="1">
@@ -6089,17 +6089,17 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A260" s="2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A260" s="12">
         <v>44166</v>
       </c>
-      <c r="B260" s="2">
+      <c r="B260" s="12">
         <v>44209</v>
       </c>
-      <c r="C260" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D260" s="5" t="s">
+      <c r="C260" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D260" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E260" s="1">
@@ -6109,17 +6109,17 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A261" s="2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A261" s="12">
         <v>44197</v>
       </c>
-      <c r="B261" s="2">
+      <c r="B261" s="12">
         <v>44237</v>
       </c>
-      <c r="C261" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D261" s="5" t="s">
+      <c r="C261" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D261" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E261" s="1">
@@ -6129,17 +6129,17 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A262" s="2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A262" s="12">
         <v>44228</v>
       </c>
-      <c r="B262" s="2">
+      <c r="B262" s="12">
         <v>44272</v>
       </c>
-      <c r="C262" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D262" s="5" t="s">
+      <c r="C262" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D262" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E262" s="1">
@@ -6152,17 +6152,17 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A263" s="2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A263" s="12">
         <v>44256</v>
       </c>
-      <c r="B263" s="2">
+      <c r="B263" s="12">
         <v>44300</v>
       </c>
-      <c r="C263" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D263" s="5" t="s">
+      <c r="C263" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D263" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E263" s="1">
@@ -6172,17 +6172,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A264" s="2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A264" s="12">
         <v>44287</v>
       </c>
-      <c r="B264" s="2">
+      <c r="B264" s="12">
         <v>44328</v>
       </c>
-      <c r="C264" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D264" s="5" t="s">
+      <c r="C264" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D264" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E264" s="1">
@@ -6192,17 +6192,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A265" s="2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A265" s="12">
         <v>44317</v>
       </c>
-      <c r="B265" s="2">
+      <c r="B265" s="12">
         <v>44356</v>
       </c>
-      <c r="C265" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D265" s="5" t="s">
+      <c r="C265" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D265" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E265" s="1">
@@ -6212,17 +6212,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A266" s="2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A266" s="12">
         <v>44348</v>
       </c>
-      <c r="B266" s="2">
+      <c r="B266" s="12">
         <v>44391</v>
       </c>
-      <c r="C266" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D266" s="5" t="s">
+      <c r="C266" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D266" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E266" s="1">
@@ -6232,17 +6232,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A267" s="2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A267" s="12">
         <v>44378</v>
       </c>
-      <c r="B267" s="2">
+      <c r="B267" s="12">
         <v>44419</v>
       </c>
-      <c r="C267" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D267" s="5" t="s">
+      <c r="C267" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D267" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E267" s="1">
@@ -6252,17 +6252,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A268" s="2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A268" s="12">
         <v>44409</v>
       </c>
-      <c r="B268" s="2">
+      <c r="B268" s="12">
         <v>44454</v>
       </c>
-      <c r="C268" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D268" s="5" t="s">
+      <c r="C268" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D268" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E268" s="1">
@@ -6272,17 +6272,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A269" s="2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A269" s="12">
         <v>44440</v>
       </c>
-      <c r="B269" s="2">
+      <c r="B269" s="12">
         <v>44482</v>
       </c>
-      <c r="C269" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D269" s="5" t="s">
+      <c r="C269" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D269" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E269" s="1">
@@ -6292,17 +6292,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A270" s="2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A270" s="12">
         <v>44470</v>
       </c>
-      <c r="B270" s="2">
+      <c r="B270" s="12">
         <v>44510</v>
       </c>
-      <c r="C270" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D270" s="5" t="s">
+      <c r="C270" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D270" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E270" s="1">
@@ -6312,17 +6312,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A271" s="2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A271" s="12">
         <v>44501</v>
       </c>
-      <c r="B271" s="2">
+      <c r="B271" s="12">
         <v>44545</v>
       </c>
-      <c r="C271" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D271" s="5" t="s">
+      <c r="C271" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D271" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E271" s="1">
@@ -6332,17 +6332,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A272" s="2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272" s="12">
         <v>44531</v>
       </c>
-      <c r="B272" s="2">
+      <c r="B272" s="12">
         <v>44573</v>
       </c>
-      <c r="C272" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D272" s="5" t="s">
+      <c r="C272" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D272" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E272" s="1">
@@ -6352,17 +6352,17 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A273" s="2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A273" s="12">
         <v>44562</v>
       </c>
-      <c r="B273" s="2">
+      <c r="B273" s="12">
         <v>44608</v>
       </c>
-      <c r="C273" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D273" s="5" t="s">
+      <c r="C273" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D273" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E273" s="1">
@@ -6372,17 +6372,17 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A274" s="2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274" s="12">
         <v>44593</v>
       </c>
-      <c r="B274" s="2">
+      <c r="B274" s="12">
         <v>44636</v>
       </c>
-      <c r="C274" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D274" s="5" t="s">
+      <c r="C274" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D274" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E274" s="1">
@@ -6392,17 +6392,17 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A275" s="2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A275" s="12">
         <v>44621</v>
       </c>
-      <c r="B275" s="2">
+      <c r="B275" s="12">
         <v>44664</v>
       </c>
-      <c r="C275" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D275" s="5" t="s">
+      <c r="C275" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D275" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E275" s="1">
@@ -6412,17 +6412,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" s="2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276" s="12">
         <v>44652</v>
       </c>
-      <c r="B276" s="2">
+      <c r="B276" s="12">
         <v>44692</v>
       </c>
-      <c r="C276" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D276" s="5" t="s">
+      <c r="C276" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D276" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E276" s="1">
@@ -6432,17 +6432,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" s="2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277" s="12">
         <v>44682</v>
       </c>
-      <c r="B277" s="2">
+      <c r="B277" s="12">
         <v>44727</v>
       </c>
-      <c r="C277" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D277" s="5" t="s">
+      <c r="C277" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D277" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E277" s="1">
@@ -6452,17 +6452,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A278" s="2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278" s="12">
         <v>44713</v>
       </c>
-      <c r="B278" s="2">
+      <c r="B278" s="12">
         <v>44755</v>
       </c>
-      <c r="C278" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D278" s="5" t="s">
+      <c r="C278" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D278" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E278" s="1">
@@ -6472,17 +6472,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A279" s="2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279" s="12">
         <v>44743</v>
       </c>
-      <c r="B279" s="2">
+      <c r="B279" s="12">
         <v>44783</v>
       </c>
-      <c r="C279" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D279" s="5" t="s">
+      <c r="C279" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D279" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E279" s="1">
@@ -6492,17 +6492,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" s="2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280" s="12">
         <v>44774</v>
       </c>
-      <c r="B280" s="2">
+      <c r="B280" s="12">
         <v>44820</v>
       </c>
-      <c r="C280" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D280" s="5" t="s">
+      <c r="C280" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D280" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E280" s="1">
@@ -6512,17 +6512,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" s="2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281" s="12">
         <v>44805</v>
       </c>
-      <c r="B281" s="2">
+      <c r="B281" s="12">
         <v>44848</v>
       </c>
-      <c r="C281" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D281" s="5" t="s">
+      <c r="C281" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D281" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E281" s="1">
@@ -6532,17 +6532,17 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" s="2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282" s="12">
         <v>44835</v>
       </c>
-      <c r="B282" s="2">
+      <c r="B282" s="12">
         <v>44874</v>
       </c>
-      <c r="C282" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D282" s="5" t="s">
+      <c r="C282" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D282" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E282" s="1">
@@ -6552,17 +6552,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A283" s="2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283" s="12">
         <v>44866</v>
       </c>
-      <c r="B283" s="2">
+      <c r="B283" s="12">
         <v>44909</v>
       </c>
-      <c r="C283" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D283" s="5" t="s">
+      <c r="C283" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D283" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E283" s="1">
@@ -6572,17 +6572,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A284" s="2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284" s="12">
         <v>44896</v>
       </c>
-      <c r="B284" s="2">
+      <c r="B284" s="12">
         <v>44937</v>
       </c>
-      <c r="C284" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D284" s="5" t="s">
+      <c r="C284" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D284" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E284" s="1">
@@ -6592,17 +6592,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A285" s="2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285" s="12">
         <v>44927</v>
       </c>
-      <c r="B285" s="2">
+      <c r="B285" s="12">
         <v>44972</v>
       </c>
-      <c r="C285" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D285" s="5" t="s">
+      <c r="C285" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D285" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E285" s="1">
@@ -6612,17 +6612,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A286" s="2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286" s="12">
         <v>44958</v>
       </c>
-      <c r="B286" s="2">
+      <c r="B286" s="12">
         <v>45000</v>
       </c>
-      <c r="C286" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D286" s="5" t="s">
+      <c r="C286" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D286" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E286" s="1">
@@ -6632,17 +6632,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A287" s="2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287" s="12">
         <v>44986</v>
       </c>
-      <c r="B287" s="2">
+      <c r="B287" s="12">
         <v>45028</v>
       </c>
-      <c r="C287" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D287" s="5" t="s">
+      <c r="C287" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D287" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E287" s="1">
@@ -6655,17 +6655,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A288" s="2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288" s="12">
         <v>45017</v>
       </c>
-      <c r="B288" s="2">
+      <c r="B288" s="12">
         <v>45056</v>
       </c>
-      <c r="C288" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D288" s="5" t="s">
+      <c r="C288" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D288" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E288" s="1">
@@ -6678,17 +6678,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A289" s="2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A289" s="12">
         <v>45047</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289" s="12">
         <v>45091</v>
       </c>
-      <c r="C289" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D289" s="5" t="s">
+      <c r="C289" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D289" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E289" s="1">
@@ -6701,17 +6701,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" s="2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A290" s="12">
         <v>45078</v>
       </c>
-      <c r="B290" s="2">
+      <c r="B290" s="12">
         <v>45119</v>
       </c>
-      <c r="C290" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D290" s="5" t="s">
+      <c r="C290" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D290" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E290" s="1">
@@ -6724,17 +6724,17 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A291" s="2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A291" s="12">
         <v>45108</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291" s="12">
         <v>45147</v>
       </c>
-      <c r="C291" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D291" s="5" t="s">
+      <c r="C291" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D291" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E291" s="1">
@@ -6747,17 +6747,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A292" s="2">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A292" s="12">
         <v>45139</v>
       </c>
-      <c r="B292" s="2">
+      <c r="B292" s="12">
         <v>45182</v>
       </c>
-      <c r="C292" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D292" s="5" t="s">
+      <c r="C292" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D292" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E292" s="1">
@@ -6767,17 +6767,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" s="2">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A293" s="12">
         <v>45170</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293" s="12">
         <v>45212</v>
       </c>
-      <c r="C293" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D293" s="5" t="s">
+      <c r="C293" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D293" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E293" s="1">
@@ -6787,17 +6787,17 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="2">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A294" s="12">
         <v>45200</v>
       </c>
-      <c r="B294" s="2">
+      <c r="B294" s="12">
         <v>45245</v>
       </c>
-      <c r="C294" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D294" s="5" t="s">
+      <c r="C294" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D294" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E294" s="1">
@@ -6810,17 +6810,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A295" s="2">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A295" s="12">
         <v>45231</v>
       </c>
-      <c r="B295" s="2">
+      <c r="B295" s="12">
         <v>45273</v>
       </c>
-      <c r="C295" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D295" s="5" t="s">
+      <c r="C295" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D295" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E295" s="1">
@@ -6830,17 +6830,17 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296" s="2">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A296" s="12">
         <v>45261</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B296" s="12">
         <v>45301</v>
       </c>
-      <c r="C296" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D296" s="5" t="s">
+      <c r="C296" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D296" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E296" s="1">
@@ -6850,17 +6850,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" s="2">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A297" s="12">
         <v>45292</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B297" s="12">
         <v>45338</v>
       </c>
-      <c r="C297" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D297" s="5" t="s">
+      <c r="C297" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D297" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E297" s="1">
@@ -6870,17 +6870,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" s="2">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A298" s="12">
         <v>45323</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B298" s="12">
         <v>45364</v>
       </c>
-      <c r="C298" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D298" s="5" t="s">
+      <c r="C298" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D298" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E298" s="1">
@@ -6890,17 +6890,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A299" s="2">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A299" s="12">
         <v>45352</v>
       </c>
-      <c r="B299" s="2">
+      <c r="B299" s="12">
         <v>45394</v>
       </c>
-      <c r="C299" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D299" s="5" t="s">
+      <c r="C299" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D299" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E299" s="1">
@@ -6910,17 +6910,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A300" s="2">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A300" s="12">
         <v>45383</v>
       </c>
-      <c r="B300" s="2">
+      <c r="B300" s="12">
         <v>45429</v>
       </c>
-      <c r="C300" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D300" s="5" t="s">
+      <c r="C300" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D300" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E300" s="1">
@@ -6930,17 +6930,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A301" s="2">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A301" s="12">
         <v>45413</v>
       </c>
-      <c r="B301" s="2">
+      <c r="B301" s="12">
         <v>45455</v>
       </c>
-      <c r="C301" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D301" s="5" t="s">
+      <c r="C301" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D301" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E301" s="1">
@@ -6950,17 +6950,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A302" s="2">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A302" s="12">
         <v>45444</v>
       </c>
-      <c r="B302" s="2">
+      <c r="B302" s="12">
         <v>45483</v>
       </c>
-      <c r="C302" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D302" s="5" t="s">
+      <c r="C302" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D302" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E302" s="1">
@@ -6970,17 +6970,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A303" s="2">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A303" s="12">
         <v>45474</v>
       </c>
-      <c r="B303" s="2">
+      <c r="B303" s="12">
         <v>45518</v>
       </c>
-      <c r="C303" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D303" s="5" t="s">
+      <c r="C303" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D303" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E303" s="1">
@@ -6990,17 +6990,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A304" s="2">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A304" s="12">
         <v>45505</v>
       </c>
-      <c r="B304" s="2">
+      <c r="B304" s="12">
         <v>45546</v>
       </c>
-      <c r="C304" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D304" s="5" t="s">
+      <c r="C304" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D304" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E304" s="1">
@@ -7010,17 +7010,17 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A305" s="2">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A305" s="12">
         <v>45536</v>
       </c>
-      <c r="B305" s="2">
+      <c r="B305" s="12">
         <v>45581</v>
       </c>
-      <c r="C305" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D305" s="5" t="s">
+      <c r="C305" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D305" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E305" s="1">
@@ -7030,17 +7030,17 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A306" s="2">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A306" s="12">
         <v>45566</v>
       </c>
-      <c r="B306" s="2">
+      <c r="B306" s="12">
         <v>45609</v>
       </c>
-      <c r="C306" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D306" s="5" t="s">
+      <c r="C306" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D306" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E306" s="1">
@@ -7050,17 +7050,17 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="2">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A307" s="12">
         <v>45597</v>
       </c>
-      <c r="B307" s="2">
+      <c r="B307" s="12">
         <v>45637</v>
       </c>
-      <c r="C307" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D307" s="5" t="s">
+      <c r="C307" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D307" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E307" s="1">
@@ -7070,17 +7070,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A308" s="2">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A308" s="12">
         <v>45627</v>
       </c>
-      <c r="B308" s="2">
+      <c r="B308" s="12">
         <v>45672</v>
       </c>
-      <c r="C308" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D308" s="5" t="s">
+      <c r="C308" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D308" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E308" s="1">
@@ -7090,17 +7090,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A309" s="2">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A309" s="12">
         <v>45658</v>
       </c>
-      <c r="B309" s="2">
+      <c r="B309" s="12">
         <v>45702</v>
       </c>
-      <c r="C309" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D309" s="5" t="s">
+      <c r="C309" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D309" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E309" s="1">
@@ -7110,17 +7110,17 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A310" s="2">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A310" s="12">
         <v>45689</v>
       </c>
-      <c r="B310" s="2">
+      <c r="B310" s="12">
         <v>45728</v>
       </c>
-      <c r="C310" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D310" s="5" t="s">
+      <c r="C310" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D310" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E310" s="1">
@@ -7130,17 +7130,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A311" s="2">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A311" s="12">
         <v>45717</v>
       </c>
-      <c r="B311" s="2">
+      <c r="B311" s="12">
         <v>45756</v>
       </c>
-      <c r="C311" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D311" s="5" t="s">
+      <c r="C311" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D311" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E311" s="1">
@@ -7150,17 +7150,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A312" s="2">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A312" s="12">
         <v>45748</v>
       </c>
-      <c r="B312" s="2">
+      <c r="B312" s="12">
         <v>45791</v>
       </c>
-      <c r="C312" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D312" s="5" t="s">
+      <c r="C312" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D312" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E312" s="1">
@@ -7170,17 +7170,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A313" s="2">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A313" s="12">
         <v>45778</v>
       </c>
-      <c r="B313" s="2">
+      <c r="B313" s="12">
         <v>45819</v>
       </c>
-      <c r="C313" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D313" s="5" t="s">
+      <c r="C313" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D313" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E313" s="1">
@@ -7190,17 +7190,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A314" s="2">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A314" s="12">
         <v>45809</v>
       </c>
-      <c r="B314" s="2">
+      <c r="B314" s="12">
         <v>45854</v>
       </c>
-      <c r="C314" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D314" s="5" t="s">
+      <c r="C314" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D314" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E314" s="1">
@@ -7210,17 +7210,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="2">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A315" s="12">
         <v>45839</v>
       </c>
-      <c r="B315" s="2">
+      <c r="B315" s="12">
         <v>45882</v>
       </c>
-      <c r="C315" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D315" s="5" t="s">
+      <c r="C315" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D315" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E315" s="1">
@@ -7230,17 +7230,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="2">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A316" s="12">
         <v>45870</v>
       </c>
-      <c r="B316" s="2">
+      <c r="B316" s="12">
         <v>45910</v>
       </c>
-      <c r="C316" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D316" s="5" t="s">
+      <c r="C316" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D316" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E316" s="1">
@@ -7250,17 +7250,17 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A317" s="2">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A317" s="12">
         <v>45901</v>
       </c>
-      <c r="B317" s="2">
+      <c r="B317" s="12">
         <v>45947</v>
       </c>
-      <c r="C317" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D317" s="5" t="s">
+      <c r="C317" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D317" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E317" s="1">
@@ -7270,17 +7270,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A318" s="2">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A318" s="12">
         <v>45931</v>
       </c>
-      <c r="B318" s="2">
+      <c r="B318" s="12">
         <v>45973</v>
       </c>
-      <c r="C318" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D318" s="5" t="s">
+      <c r="C318" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D318" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E318" s="1">
@@ -7290,17 +7290,17 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A319" s="2">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A319" s="12">
         <v>45962</v>
       </c>
-      <c r="B319" s="2">
+      <c r="B319" s="12">
         <v>46001</v>
       </c>
-      <c r="C319" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D319" s="5" t="s">
+      <c r="C319" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D319" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E319" s="1">
@@ -7310,17 +7310,17 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A320" s="2">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A320" s="12">
         <v>45992</v>
       </c>
-      <c r="B320" s="2">
+      <c r="B320" s="12">
         <v>46036</v>
       </c>
-      <c r="C320" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D320" s="5" t="s">
+      <c r="C320" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D320" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E320" s="1">
@@ -7330,17 +7330,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A321" s="2">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A321" s="12">
         <v>46023</v>
       </c>
-      <c r="B321" s="2">
+      <c r="B321" s="12">
         <v>46064</v>
       </c>
-      <c r="C321" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D321" s="5" t="s">
+      <c r="C321" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D321" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E321" s="1">
@@ -7350,17 +7350,17 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A322" s="2">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A322" s="12">
         <v>46054</v>
       </c>
-      <c r="B322" s="2">
+      <c r="B322" s="12">
         <v>46099</v>
       </c>
-      <c r="C322" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D322" s="5" t="s">
+      <c r="C322" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D322" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E322" s="1">
@@ -7370,17 +7370,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A323" s="2">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A323" s="12">
         <v>46082</v>
       </c>
-      <c r="B323" s="2">
+      <c r="B323" s="12">
         <v>46127</v>
       </c>
-      <c r="C323" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D323" s="5" t="s">
+      <c r="C323" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D323" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E323" s="1">
@@ -7390,17 +7390,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A324" s="2">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A324" s="12">
         <v>46113</v>
       </c>
-      <c r="B324" s="2">
+      <c r="B324" s="12">
         <v>46155</v>
       </c>
-      <c r="C324" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D324" s="5" t="s">
+      <c r="C324" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D324" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E324" s="1">
@@ -7410,17 +7410,17 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A325" s="2">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A325" s="12">
         <v>46143</v>
       </c>
-      <c r="B325" s="2">
+      <c r="B325" s="12">
         <v>46184</v>
       </c>
-      <c r="C325" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D325" s="5" t="s">
+      <c r="C325" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D325" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E325" s="1">
@@ -7430,17 +7430,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A326" s="2">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A326" s="12">
         <v>46174</v>
       </c>
-      <c r="B326" s="2">
+      <c r="B326" s="12">
         <v>46218</v>
       </c>
-      <c r="C326" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D326" s="5" t="s">
+      <c r="C326" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D326" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E326" s="1">
@@ -7450,17 +7450,17 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A327" s="2">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A327" s="12">
         <v>46204</v>
       </c>
-      <c r="B327" s="2">
+      <c r="B327" s="12">
         <v>46246</v>
       </c>
-      <c r="C327" s="3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D327" s="5" t="s">
+      <c r="C327" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D327" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E327" s="1">
